--- a/custom-products.xlsx
+++ b/custom-products.xlsx
@@ -675,17 +675,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>LOCAL-001</t>
+          <t>31-069</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Local Supplier Trucker Hat</t>
+          <t>OTTO CAP 5 Panel Mid Profile Baseball Cap</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Local Supplier</t>
+          <t>OTTO CAP</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -695,25 +695,23 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Trucker Hat</t>
+          <t>Baseball Caps</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Foam-front, mesh-back, snapback.</t>
+          <t>65/35 polyester/cotton twill. Structured firm front panel. Mid profile. Pre-curved visor. Adjustable snapback. One size fits most.</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>6.5</v>
+        <v>5.05</v>
       </c>
       <c r="H2" s="2" t="n"/>
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
-      <c r="K2" s="2" t="n">
-        <v>12</v>
-      </c>
+      <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
@@ -725,88 +723,34 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>OS</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr"/>
+          <t>OSFA</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>[{"name":"Black","code":"BK","hex":"#000000","images":{"front_model":"https://example.com/local-001-black-front.jpg","back_model":"https://example.com/local-001-black-back.jpg","front_flat":null,"back_flat":null,"side_model":null}},{"name":"White","code":"WH","hex":"#FFFFFF","images":{"front_model":"https://example.com/local-001-white-front.jpg","back_model":null,"front_flat":null,"back_flat":null,"side_model":null}}]</t>
+          <t>[{"name": "Black", "code": "003", "hex": "#000000", "images": {"front_model": "https://aliveprintshop.github.io/PriceCalculator/media/otto-31069-black-front.jpg", "back_model": "https://aliveprintshop.github.io/PriceCalculator/media/otto-31069-black-back.jpg", "front_flat": "https://aliveprintshop.github.io/PriceCalculator/media/otto-31069-black-front.jpg", "back_flat": "https://aliveprintshop.github.io/PriceCalculator/media/otto-31069-black-back.jpg", "side_model": null}}]</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>LOCAL-002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Seasonal Clearance Tote</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Local Supplier</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Bags</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tote</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Canvas tote, 12oz. Limited time pricing.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>OS</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>[{"name":"Navy","code":"NVY","hex":"#1B2C55","images":{"front_model":"https://example.com/local-002-navy-front.jpg","back_model":null,"front_flat":null,"back_flat":null,"side_model":null}}]</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/custom-products.xlsx
+++ b/custom-products.xlsx
@@ -729,7 +729,7 @@
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>[{"name": "Black", "code": "003", "hex": "#000000", "images": {"front_model": "https://aliveprintshop.github.io/PriceCalculator/media/otto-31069-black-front.jpg", "back_model": "https://aliveprintshop.github.io/PriceCalculator/media/otto-31069-black-back.jpg", "front_flat": "https://aliveprintshop.github.io/PriceCalculator/media/otto-31069-black-front.jpg", "back_flat": "https://aliveprintshop.github.io/PriceCalculator/media/otto-31069-black-back.jpg", "side_model": null}}]</t>
+          <t>[{"name": "Royal", "code": "001", "hex": "#21397D", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-001-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-001-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-001-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-001-B.medium.jpg", "side_model": null}}, {"name": "Red", "code": "002", "hex": "#D20D38", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-002-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-002-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-002-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-002-B.medium.jpg", "side_model": null}}, {"name": "Black", "code": "003", "hex": "#24252B", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-003-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-003-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-003-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-003-B.medium.jpg", "side_model": null}}, {"name": "Navy", "code": "004", "hex": "#1E2139", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-004-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-004-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-004-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-004-B.medium.jpg", "side_model": null}}, {"name": "Maroon", "code": "010", "hex": "#5B132E", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-010-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-010-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-010-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-010-B.medium.jpg", "side_model": null}}, {"name": "Gray", "code": "014", "hex": "#A297A5", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-014-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-014-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-014-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-014-B.medium.jpg", "side_model": null}}, {"name": "White", "code": "016", "hex": "#E3E4EF", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-016-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-016-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-016-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-016-B.medium.jpg", "side_model": null}}, {"name": "Dark Green", "code": "017", "hex": "#1B2E2D", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-017-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-017-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-017-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-017-B.medium.jpg", "side_model": null}}, {"name": "Yellow", "code": "020", "hex": "#FAD253", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-020-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-020-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-020-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-020-B.medium.jpg", "side_model": null}}, {"name": "Charcoal Gray", "code": "025", "hex": "#605A64", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-025-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-025-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-025-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-025-B.medium.jpg", "side_model": null}}, {"name": "Khaki", "code": "032", "hex": "#D3BFB4", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-032-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-032-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-032-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-032-B.medium.jpg", "side_model": null}}, {"name": "Dark Brown", "code": "039", "hex": "#523C3C", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-039-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-039-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-039-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-039-B.medium.jpg", "side_model": null}}, {"name": "Pink", "code": "050", "hex": "#E7AAC0", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-050-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-050-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-050-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-050-B.medium.jpg", "side_model": null}}, {"name": "Royal/Black", "code": "0103", "hex": "#1D1E24", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0103-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0103-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0103-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0103-B.medium.jpg", "side_model": null}}, {"name": "Royal/Gray", "code": "0114", "hex": "#9C919F", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0114-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0114-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0114-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0114-B.medium.jpg", "side_model": null}}, {"name": "Royal/White", "code": "0116", "hex": "#DFE1ED", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0116-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0116-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0116-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0116-B.medium.jpg", "side_model": null}}, {"name": "Royal/Natural", "code": "0131", "hex": "#DBCECC", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0131-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0131-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0131-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0131-B.medium.jpg", "side_model": null}}, {"name": "Red/Royal", "code": "0201", "hex": "#0E499D", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0201-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0201-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0201-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0201-B.medium.jpg", "side_model": null}}, {"name": "Red/Black", "code": "0203", "hex": "#16181E", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0203-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0203-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0203-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0203-B.medium.jpg", "side_model": null}}, {"name": "Red/Navy", "code": "0204", "hex": "#1F213A", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0204-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0204-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0204-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0204-B.medium.jpg", "side_model": null}}, {"name": "Red/Gray", "code": "0214", "hex": "#ACA0AE", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0214-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0214-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0214-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0214-B.medium.jpg", "side_model": null}}, {"name": "Red/White", "code": "0216", "hex": "#E1E2ED", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0216-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0216-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0216-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0216-B.medium.jpg", "side_model": null}}, {"name": "Red/Natural", "code": "0231", "hex": "#D6C8C5", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0231-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0231-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0231-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0231-B.medium.jpg", "side_model": null}}, {"name": "Red/Khaki", "code": "0232", "hex": "#BFA99D", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0232-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0232-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0232-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0232-B.medium.jpg", "side_model": null}}, {"name": "Black/Red", "code": "0302", "hex": "#C70832", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0302-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0302-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0302-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0302-B.medium.jpg", "side_model": null}}, {"name": "Black/Gray", "code": "0314", "hex": "#ACA1AE", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0314-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0314-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0314-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0314-B.medium.jpg", "side_model": null}}, {"name": "Black/White", "code": "0316", "hex": "#E2E3EE", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0316-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0316-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0316-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0316-B.medium.jpg", "side_model": null}}, {"name": "Black/Charcoal Gray", "code": "0325", "hex": "#544D57", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0325-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0325-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0325-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0325-B.medium.jpg", "side_model": null}}, {"name": "Black/Natural", "code": "0331", "hex": "#D7CAC8", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0331-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0331-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0331-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0331-B.medium.jpg", "side_model": null}}, {"name": "Black/Khaki", "code": "0332", "hex": "#CFB8AB", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0332-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0332-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0332-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0332-B.medium.jpg", "side_model": null}}, {"name": "Navy/Gray", "code": "0414", "hex": "#B6AFBD", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0414-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0414-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0414-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0414-B.medium.jpg", "side_model": null}}, {"name": "Navy/White", "code": "0416", "hex": "#E2E3ED", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0416-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0416-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0416-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0416-B.medium.jpg", "side_model": null}}, {"name": "Navy/Natural", "code": "0431", "hex": "#D5C9C8", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0431-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0431-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0431-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0431-B.medium.jpg", "side_model": null}}, {"name": "Navy/Khaki", "code": "0432", "hex": "#CBB7AA", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0432-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0432-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0432-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0432-B.medium.jpg", "side_model": null}}, {"name": "Col.Blue/Natural", "code": "0831", "hex": "#E2DAD8", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0831-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0831-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0831-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-0831-B.medium.jpg", "side_model": null}}, {"name": "Maroon/Gray", "code": "1014", "hex": "#A79CAA", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1014-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1014-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1014-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1014-B.medium.jpg", "side_model": null}}, {"name": "Maroon/White", "code": "1016", "hex": "#DDDEEB", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1016-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1016-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1016-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1016-B.medium.jpg", "side_model": null}}, {"name": "Maroon/Khaki", "code": "1032", "hex": "#BDA99F", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1032-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1032-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1032-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1032-B.medium.jpg", "side_model": null}}, {"name": "Lavender/Natural", "code": "1331", "hex": "#EBE4DB", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1331-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1331-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1331-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1331-B.medium.jpg", "side_model": null}}, {"name": "Gray/Royal", "code": "1401", "hex": "#0E4293", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1401-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1401-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1401-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1401-B.medium.jpg", "side_model": null}}, {"name": "Gray/Navy", "code": "1404", "hex": "#1A1D34", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1404-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1404-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1404-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1404-B.medium.jpg", "side_model": null}}, {"name": "Dark Green/White", "code": "1716", "hex": "#E0E2ED", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1716-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1716-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1716-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1716-B.medium.jpg", "side_model": null}}, {"name": "Dark Green/Natural", "code": "1731", "hex": "#D8CECC", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1731-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1731-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1731-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1731-B.medium.jpg", "side_model": null}}, {"name": "Dark Green/Khaki", "code": "1732", "hex": "#C2AB9E", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1732-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1732-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1732-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-1732-B.medium.jpg", "side_model": null}}, {"name": "Khaki/Black", "code": "3203", "hex": "#1A191F", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3203-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3203-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3203-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3203-B.medium.jpg", "side_model": null}}, {"name": "Khaki/Navy", "code": "3204", "hex": "#1B1D33", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3204-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3204-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3204-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3204-B.medium.jpg", "side_model": null}}, {"name": "Khaki/Dark Green", "code": "3217", "hex": "#1B2C2B", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3217-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3217-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3217-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3217-B.medium.jpg", "side_model": null}}, {"name": "Khaki/Natural", "code": "3231", "hex": "#F3E7D3", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3231-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3231-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3231-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3231-B.medium.jpg", "side_model": null}}, {"name": "Dark Brown/Natural", "code": "3931", "hex": "#D1C2AC", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3931-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3931-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3931-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-3931-B.medium.jpg", "side_model": null}}, {"name": "Pink/Natural", "code": "5031", "hex": "#E5DEDB", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-5031-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-5031-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-5031-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-5031-B.medium.jpg", "side_model": null}}, {"name": "Caribbean Green/Natural", "code": "5131", "hex": "#ECE1CE", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-5131-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-5131-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-5131-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-5131-B.medium.jpg", "side_model": null}}, {"name": "Sage Green/Natural", "code": "6131", "hex": "#E7DFCD", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-6131-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-6131-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-6131-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-6131-B.medium.jpg", "side_model": null}}, {"name": "Neon Orange", "code": "009", "hex": "#FE7435", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-009-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-009-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-009-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-009-B.medium.jpg", "side_model": null}}, {"name": "Neon Yellow", "code": "040", "hex": "#DAF960", "images": {"front_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-040-F.medium.jpg", "back_model": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-040-B.medium.jpg", "front_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-040-F.medium.jpg", "back_flat": "https://s3-us-west-2.amazonaws.com/ottocap/media/products/otto/31-069/31-069-040-B.medium.jpg", "side_model": null}}]</t>
         </is>
       </c>
     </row>
